--- a/diseases/d242/2026-2029.xlsx
+++ b/diseases/d242/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>4</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.07075903303182025</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>4</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.07075903303182025</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>6</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.1061385495477304</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>3</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.05306927477386519</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -3535,9 +3514,6 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">

--- a/diseases/d242/2026-2029.xlsx
+++ b/diseases/d242/2026-2029.xlsx
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d242/2026-2029.xlsx
+++ b/diseases/d242/2026-2029.xlsx
@@ -3511,13 +3511,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3670,10 +3670,10 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d242/2026-2029.xlsx
+++ b/diseases/d242/2026-2029.xlsx
@@ -790,7 +790,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -798,17 +798,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS2" t="inlineStr">
         <is>
           <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -1024,7 +1029,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1032,17 +1037,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1183,7 +1193,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1191,17 +1201,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1417,7 +1432,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1425,17 +1440,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1576,7 +1596,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1584,17 +1604,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1810,7 +1835,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1818,17 +1843,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1969,7 +1999,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1977,17 +2007,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2203,7 +2238,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2211,17 +2246,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2362,7 +2402,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2370,17 +2410,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2596,7 +2641,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2604,17 +2649,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2755,7 +2805,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2763,17 +2813,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -2989,7 +3044,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -2997,17 +3052,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -3148,7 +3208,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -3156,17 +3216,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -3382,7 +3447,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -3390,17 +3455,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -3541,7 +3611,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -3549,17 +3619,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -3775,7 +3850,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -3783,17 +3858,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">

--- a/diseases/d242/2026-2029.xlsx
+++ b/diseases/d242/2026-2029.xlsx
@@ -3917,6 +3917,409 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Lymfogranuloma venerum (LGV)</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; Kept distinct from general genital chlamydia code 904 to prevent double counting.</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3950,7 +4353,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4436,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -4043,7 +4446,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -4063,7 +4466,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
